--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260811.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260811.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>遠東銀</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>99,084,000</t>
+          <t>8,422,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>遠東銀</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>8,422,000</t>
+          <t>99,084,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>8,032,000</t>
+          <t>28,042,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>28,042,000</t>
+          <t>8,032,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>12,795,000</t>
+          <t>2,276,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2,276,000</t>
+          <t>12,795,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>16,660,000</t>
+          <t>2,115,678</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>17,902,000</t>
+          <t>16,660,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>2,115,678</t>
+          <t>17,902,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
